--- a/artfynd/A 29995-2025 artfynd.xlsx
+++ b/artfynd/A 29995-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>76214262</v>
       </c>
       <c r="B2" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>642365.0811911838</v>
+        <v>642365</v>
       </c>
       <c r="R2" t="n">
-        <v>7123945.128284551</v>
+        <v>7123945</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2018-09-24</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-09-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>76214457</v>
+        <v>76214389</v>
       </c>
       <c r="B3" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>642256.793232126</v>
+        <v>642265</v>
       </c>
       <c r="R3" t="n">
-        <v>7123803.205860217</v>
+        <v>7123810</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2018-09-24</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2018-09-24</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,12 +872,7 @@
         <v>76214390</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>642007.9552698748</v>
+        <v>642008</v>
       </c>
       <c r="R4" t="n">
-        <v>7123840.147779024</v>
+        <v>7123840</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +937,9 @@
           <t>2018-09-24</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2018-09-24</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,12 +969,7 @@
         <v>76214641</v>
       </c>
       <c r="B5" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>642007.9552698748</v>
+        <v>642008</v>
       </c>
       <c r="R5" t="n">
-        <v>7123840.147779024</v>
+        <v>7123840</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,19 +1034,9 @@
           <t>2018-09-24</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2018-09-24</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,37 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>76214389</v>
+        <v>76214457</v>
       </c>
       <c r="B6" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>642265.206553001</v>
+        <v>642257</v>
       </c>
       <c r="R6" t="n">
-        <v>7123810.135038082</v>
+        <v>7123803</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,19 +1131,9 @@
           <t>2018-09-24</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2018-09-24</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 29995-2025 artfynd.xlsx
+++ b/artfynd/A 29995-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76214262</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76214389</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76214390</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76214641</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,8 +1182,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76214457</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>